--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/91.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/4_fold/91.xlsx
@@ -426,13 +426,13 @@
         <v>-6.86652350301075</v>
       </c>
       <c r="E2">
-        <v>-10.15442123933322</v>
+        <v>-6.731700957907796</v>
       </c>
       <c r="F2">
-        <v>-1.578400389400784</v>
+        <v>-1.816309164219607</v>
       </c>
       <c r="G2">
-        <v>-11.37879292200195</v>
+        <v>-10.12054617182325</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-6.740426515593126</v>
       </c>
       <c r="E3">
-        <v>-10.79726529556607</v>
+        <v>-8.584145706329478</v>
       </c>
       <c r="F3">
-        <v>-1.752065130295492</v>
+        <v>-1.541895894694215</v>
       </c>
       <c r="G3">
-        <v>-11.73399499947652</v>
+        <v>-9.967083439488016</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-6.694232910443509</v>
       </c>
       <c r="E4">
-        <v>-10.75721094296823</v>
+        <v>-8.583738143668787</v>
       </c>
       <c r="F4">
-        <v>-0.9680079282391344</v>
+        <v>-1.429907248774944</v>
       </c>
       <c r="G4">
-        <v>-11.59414277416987</v>
+        <v>-9.27180571592792</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-6.732676780078137</v>
       </c>
       <c r="E5">
-        <v>-11.9560927371809</v>
+        <v>-10.28053471197283</v>
       </c>
       <c r="F5">
-        <v>-1.080516788887363</v>
+        <v>-1.062499797876474</v>
       </c>
       <c r="G5">
-        <v>-11.50557276061578</v>
+        <v>-8.990834713792669</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-6.820391911328474</v>
       </c>
       <c r="E6">
-        <v>-12.56812052779156</v>
+        <v>-10.35720177692269</v>
       </c>
       <c r="F6">
-        <v>-0.8626197137853702</v>
+        <v>-1.162209553784048</v>
       </c>
       <c r="G6">
-        <v>-11.50902788691787</v>
+        <v>-9.412990117187707</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-6.923465059216494</v>
       </c>
       <c r="E7">
-        <v>-13.15131099592137</v>
+        <v>-10.98375238367595</v>
       </c>
       <c r="F7">
-        <v>-0.5141031815077425</v>
+        <v>-1.104148454154428</v>
       </c>
       <c r="G7">
-        <v>-11.28854292300942</v>
+        <v>-8.98827864219786</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-6.999023381564093</v>
       </c>
       <c r="E8">
-        <v>-13.83757858941378</v>
+        <v>-13.07039622235232</v>
       </c>
       <c r="F8">
-        <v>0.09755585341278722</v>
+        <v>-0.6121810536318012</v>
       </c>
       <c r="G8">
-        <v>-11.24797718087001</v>
+        <v>-9.073229468371885</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-7.002936635549198</v>
       </c>
       <c r="E9">
-        <v>-14.65725049869814</v>
+        <v>-12.64819753366919</v>
       </c>
       <c r="F9">
-        <v>0.1309539703588577</v>
+        <v>-0.3256073506333122</v>
       </c>
       <c r="G9">
-        <v>-10.85011266067954</v>
+        <v>-9.949325468408302</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-6.89854295377769</v>
       </c>
       <c r="E10">
-        <v>-15.34647971419156</v>
+        <v>-13.96822506453507</v>
       </c>
       <c r="F10">
-        <v>0.167315157504742</v>
+        <v>-0.02735615235755863</v>
       </c>
       <c r="G10">
-        <v>-11.07542102028037</v>
+        <v>-8.894960701047253</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-6.650667303647221</v>
       </c>
       <c r="E11">
-        <v>-16.54468676577709</v>
+        <v>-14.45137248488742</v>
       </c>
       <c r="F11">
-        <v>0.4508951407095135</v>
+        <v>-0.03868241985603627</v>
       </c>
       <c r="G11">
-        <v>-10.12060523381132</v>
+        <v>-8.617674510723258</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-6.243281071532752</v>
       </c>
       <c r="E12">
-        <v>-17.58898004278992</v>
+        <v>-15.15106247533856</v>
       </c>
       <c r="F12">
-        <v>0.9774841568321453</v>
+        <v>0.007817155932711182</v>
       </c>
       <c r="G12">
-        <v>-9.957295555576193</v>
+        <v>-8.161699556715023</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-5.666233314163726</v>
       </c>
       <c r="E13">
-        <v>-17.62066124694758</v>
+        <v>-15.7698105213766</v>
       </c>
       <c r="F13">
-        <v>0.9749841440104964</v>
+        <v>0.6642204561154562</v>
       </c>
       <c r="G13">
-        <v>-9.018272288472746</v>
+        <v>-7.289613209424248</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-4.934859322446409</v>
       </c>
       <c r="E14">
-        <v>-18.10512645323617</v>
+        <v>-16.79705409375055</v>
       </c>
       <c r="F14">
-        <v>1.150447270536682</v>
+        <v>0.1095804346318248</v>
       </c>
       <c r="G14">
-        <v>-8.501036927949677</v>
+        <v>-7.143014792591377</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-4.075373716707394</v>
       </c>
       <c r="E15">
-        <v>-19.35277538403745</v>
+        <v>-17.21805726529565</v>
       </c>
       <c r="F15">
-        <v>1.605512559999396</v>
+        <v>0.4120910980927735</v>
       </c>
       <c r="G15">
-        <v>-8.115394958068141</v>
+        <v>-6.691308707831979</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-3.127594058553004</v>
       </c>
       <c r="E16">
-        <v>-19.63202826219445</v>
+        <v>-17.21752743383675</v>
       </c>
       <c r="F16">
-        <v>1.488015270851509</v>
+        <v>0.5854824777445576</v>
       </c>
       <c r="G16">
-        <v>-7.987496222902545</v>
+        <v>-6.108855787593388</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-2.138419609012414</v>
       </c>
       <c r="E17">
-        <v>-20.52949482645658</v>
+        <v>-19.72148826621598</v>
       </c>
       <c r="F17">
-        <v>1.556559359963557</v>
+        <v>1.192801695841821</v>
       </c>
       <c r="G17">
-        <v>-7.118021727973086</v>
+        <v>-4.966091630199339</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-1.152574232085986</v>
       </c>
       <c r="E18">
-        <v>-21.38509564851781</v>
+        <v>-19.74290341979825</v>
       </c>
       <c r="F18">
-        <v>1.885502398880434</v>
+        <v>1.112458341444297</v>
       </c>
       <c r="G18">
-        <v>-6.202600287546724</v>
+        <v>-4.018396094514279</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-0.217329787668622</v>
       </c>
       <c r="E19">
-        <v>-22.01742458810485</v>
+        <v>-21.02750017002811</v>
       </c>
       <c r="F19">
-        <v>2.127591115613785</v>
+        <v>1.023274650124096</v>
       </c>
       <c r="G19">
-        <v>-5.680767935618874</v>
+        <v>-4.104646284425843</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.6335100095204917</v>
       </c>
       <c r="E20">
-        <v>-23.469860170481</v>
+        <v>-21.69232091062019</v>
       </c>
       <c r="F20">
-        <v>2.450177263081579</v>
+        <v>1.434337063150101</v>
       </c>
       <c r="G20">
-        <v>-5.059941129242577</v>
+        <v>-3.781311430736601</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.369041048268761</v>
       </c>
       <c r="E21">
-        <v>-24.41204541556887</v>
+        <v>-22.60592695624566</v>
       </c>
       <c r="F21">
-        <v>2.513113304876674</v>
+        <v>1.710504814834622</v>
       </c>
       <c r="G21">
-        <v>-4.728061974612541</v>
+        <v>-2.145579827473137</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.977270352765264</v>
       </c>
       <c r="E22">
-        <v>-24.3413332939391</v>
+        <v>-22.42734658375318</v>
       </c>
       <c r="F22">
-        <v>2.099156576145289</v>
+        <v>1.794395238450934</v>
       </c>
       <c r="G22">
-        <v>-4.41465281614062</v>
+        <v>-2.908401496834404</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>2.446389178069899</v>
       </c>
       <c r="E23">
-        <v>-24.73437766696084</v>
+        <v>-23.70152784376539</v>
       </c>
       <c r="F23">
-        <v>2.333514968275713</v>
+        <v>1.507935850154031</v>
       </c>
       <c r="G23">
-        <v>-3.103880271238323</v>
+        <v>-2.22167135543666</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>2.778679886782955</v>
       </c>
       <c r="E24">
-        <v>-25.82715278669979</v>
+        <v>-24.02177246863983</v>
       </c>
       <c r="F24">
-        <v>2.401716113283002</v>
+        <v>1.763959363337274</v>
       </c>
       <c r="G24">
-        <v>-3.228740595239873</v>
+        <v>-1.902100062876102</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>2.971059278366932</v>
       </c>
       <c r="E25">
-        <v>-25.92061143327009</v>
+        <v>-23.77989761494214</v>
       </c>
       <c r="F25">
-        <v>2.490367992730606</v>
+        <v>2.05244659503623</v>
       </c>
       <c r="G25">
-        <v>-2.497284122765338</v>
+        <v>-1.889631420950212</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>3.029320455802491</v>
       </c>
       <c r="E26">
-        <v>-25.94474819973097</v>
+        <v>-24.22161855507233</v>
       </c>
       <c r="F26">
-        <v>2.408081288406114</v>
+        <v>2.035195015505527</v>
       </c>
       <c r="G26">
-        <v>-3.466140256287257</v>
+        <v>-1.368957340232846</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>2.964568817566895</v>
       </c>
       <c r="E27">
-        <v>-26.94913656378821</v>
+        <v>-25.54991960795021</v>
       </c>
       <c r="F27">
-        <v>1.940621965862714</v>
+        <v>1.813812170372554</v>
       </c>
       <c r="G27">
-        <v>-2.719045481860409</v>
+        <v>-2.741781066045802</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>2.799357313802907</v>
       </c>
       <c r="E28">
-        <v>-26.55880021822306</v>
+        <v>-24.21316842257401</v>
       </c>
       <c r="F28">
-        <v>2.043576436887053</v>
+        <v>1.641460391811283</v>
       </c>
       <c r="G28">
-        <v>-2.823398171115429</v>
+        <v>-2.559709362933774</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>2.564922760873688</v>
       </c>
       <c r="E29">
-        <v>-26.52392643988999</v>
+        <v>-23.95572920371196</v>
       </c>
       <c r="F29">
-        <v>2.359028684281938</v>
+        <v>2.015213137015198</v>
       </c>
       <c r="G29">
-        <v>-2.95020097828017</v>
+        <v>-2.537196901814423</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>2.295224116009766</v>
       </c>
       <c r="E30">
-        <v>-26.99656780054455</v>
+        <v>-23.65014777767437</v>
       </c>
       <c r="F30">
-        <v>2.028531628117408</v>
+        <v>1.899004787546066</v>
       </c>
       <c r="G30">
-        <v>-3.56303472893766</v>
+        <v>-3.043879853802317</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>2.017670118846791</v>
       </c>
       <c r="E31">
-        <v>-25.64523492886366</v>
+        <v>-24.19857315084729</v>
       </c>
       <c r="F31">
-        <v>1.916894209976925</v>
+        <v>1.619165711532337</v>
       </c>
       <c r="G31">
-        <v>-3.261861245660908</v>
+        <v>-2.687204507847558</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.749591607066889</v>
       </c>
       <c r="E32">
-        <v>-26.01319608435691</v>
+        <v>-22.16143459002278</v>
       </c>
       <c r="F32">
-        <v>1.938850916355528</v>
+        <v>1.453992564883727</v>
       </c>
       <c r="G32">
-        <v>-3.446620269230121</v>
+        <v>-2.550768034184287</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.495993128387225</v>
       </c>
       <c r="E33">
-        <v>-26.1002695825764</v>
+        <v>-23.51389505173158</v>
       </c>
       <c r="F33">
-        <v>2.08256603380202</v>
+        <v>1.924430696607595</v>
       </c>
       <c r="G33">
-        <v>-3.667997725402737</v>
+        <v>-2.653673704731592</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.256436799053274</v>
       </c>
       <c r="E34">
-        <v>-25.55973733959884</v>
+        <v>-22.80318275554577</v>
       </c>
       <c r="F34">
-        <v>2.13110505013646</v>
+        <v>2.155621411789714</v>
       </c>
       <c r="G34">
-        <v>-3.390629504539756</v>
+        <v>-3.020911302886204</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.022930262267021</v>
       </c>
       <c r="E35">
-        <v>-24.84988092500048</v>
+        <v>-23.72418832769977</v>
       </c>
       <c r="F35">
-        <v>1.806118293935352</v>
+        <v>1.813117998489008</v>
       </c>
       <c r="G35">
-        <v>-3.847871010069937</v>
+        <v>-2.472163090506229</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>0.7879378218880967</v>
       </c>
       <c r="E36">
-        <v>-24.71382745191403</v>
+        <v>-22.10297199058375</v>
       </c>
       <c r="F36">
-        <v>2.212898047488883</v>
+        <v>1.683634233022612</v>
       </c>
       <c r="G36">
-        <v>-4.18496730697949</v>
+        <v>-3.307968971014225</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>0.5418935064010428</v>
       </c>
       <c r="E37">
-        <v>-24.05121207816369</v>
+        <v>-22.43270829697826</v>
       </c>
       <c r="F37">
-        <v>2.077966937981677</v>
+        <v>1.681331371642829</v>
       </c>
       <c r="G37">
-        <v>-3.855598286842429</v>
+        <v>-2.48681046354759</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>0.2750922512318996</v>
       </c>
       <c r="E38">
-        <v>-23.79259092758564</v>
+        <v>-21.59422057819202</v>
       </c>
       <c r="F38">
-        <v>2.244026437751283</v>
+        <v>1.80812956998935</v>
       </c>
       <c r="G38">
-        <v>-4.119585686185994</v>
+        <v>-3.993826307477157</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-0.01897216461164408</v>
       </c>
       <c r="E39">
-        <v>-23.55864090340137</v>
+        <v>-21.00931834688731</v>
       </c>
       <c r="F39">
-        <v>2.065978804928363</v>
+        <v>2.204117353019208</v>
       </c>
       <c r="G39">
-        <v>-3.808502913799719</v>
+        <v>-2.878634254847122</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-0.34812145562898</v>
       </c>
       <c r="E40">
-        <v>-23.06761393827567</v>
+        <v>-20.94189842586112</v>
       </c>
       <c r="F40">
-        <v>2.327719709925728</v>
+        <v>2.20023562336969</v>
       </c>
       <c r="G40">
-        <v>-4.388150389604985</v>
+        <v>-4.222701354913104</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-0.7115610627397918</v>
       </c>
       <c r="E41">
-        <v>-23.15459233854099</v>
+        <v>-19.94769459984713</v>
       </c>
       <c r="F41">
-        <v>2.573408511391645</v>
+        <v>2.204292966908602</v>
       </c>
       <c r="G41">
-        <v>-3.724165676057312</v>
+        <v>-3.094955348596633</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.107993597141948</v>
       </c>
       <c r="E42">
-        <v>-22.84958150022836</v>
+        <v>-19.61711146881319</v>
       </c>
       <c r="F42">
-        <v>2.639494006052184</v>
+        <v>2.256859505555453</v>
       </c>
       <c r="G42">
-        <v>-3.979244558866984</v>
+        <v>-2.524721697445415</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.526154025172987</v>
       </c>
       <c r="E43">
-        <v>-22.48565068660193</v>
+        <v>-19.59420191880838</v>
       </c>
       <c r="F43">
-        <v>2.90115538777888</v>
+        <v>2.373102646455502</v>
       </c>
       <c r="G43">
-        <v>-3.706066457935415</v>
+        <v>-2.723389819205114</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.953773593297315</v>
       </c>
       <c r="E44">
-        <v>-22.13392411042618</v>
+        <v>-18.56464429621651</v>
       </c>
       <c r="F44">
-        <v>2.700408831384448</v>
+        <v>2.485931256921211</v>
       </c>
       <c r="G44">
-        <v>-4.147732004722911</v>
+        <v>-2.339654239049614</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-2.372397156909967</v>
       </c>
       <c r="E45">
-        <v>-21.17663187604871</v>
+        <v>-18.06300258801683</v>
       </c>
       <c r="F45">
-        <v>2.785874809800884</v>
+        <v>2.357757968686044</v>
       </c>
       <c r="G45">
-        <v>-3.649649134442322</v>
+        <v>-2.791964068575949</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-2.763472985200327</v>
       </c>
       <c r="E46">
-        <v>-20.22968267630476</v>
+        <v>-17.92516942464536</v>
       </c>
       <c r="F46">
-        <v>3.123654872170828</v>
+        <v>2.209584577877685</v>
       </c>
       <c r="G46">
-        <v>-4.926529941857114</v>
+        <v>-3.215153056762212</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-3.110974224310964</v>
       </c>
       <c r="E47">
-        <v>-20.14657159284199</v>
+        <v>-17.54544782215419</v>
       </c>
       <c r="F47">
-        <v>3.045329420766523</v>
+        <v>2.600459677297466</v>
       </c>
       <c r="G47">
-        <v>-4.38262481249888</v>
+        <v>-2.714635520084515</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-3.401316692213447</v>
       </c>
       <c r="E48">
-        <v>-18.97999140372603</v>
+        <v>-15.94222311227064</v>
       </c>
       <c r="F48">
-        <v>2.734302312037393</v>
+        <v>2.499045969642333</v>
       </c>
       <c r="G48">
-        <v>-4.679513020418997</v>
+        <v>-3.571667622860559</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-3.631923398320334</v>
       </c>
       <c r="E49">
-        <v>-18.60841652597465</v>
+        <v>-17.63288359829428</v>
       </c>
       <c r="F49">
-        <v>3.096863813629486</v>
+        <v>1.997375073363313</v>
       </c>
       <c r="G49">
-        <v>-4.807894095153832</v>
+        <v>-3.443975604653208</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-3.802101307406197</v>
       </c>
       <c r="E50">
-        <v>-18.02310220353524</v>
+        <v>-15.07258402078564</v>
       </c>
       <c r="F50">
-        <v>2.942818954670084</v>
+        <v>2.167361034622189</v>
       </c>
       <c r="G50">
-        <v>-4.35609613619077</v>
+        <v>-2.892677883121545</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-3.924505293394204</v>
       </c>
       <c r="E51">
-        <v>-18.07862582334329</v>
+        <v>-14.55358467171455</v>
       </c>
       <c r="F51">
-        <v>2.475904697877726</v>
+        <v>2.594394371174167</v>
       </c>
       <c r="G51">
-        <v>-4.496575074815276</v>
+        <v>-3.621742345079245</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-4.010160001588681</v>
       </c>
       <c r="E52">
-        <v>-17.12869688770229</v>
+        <v>-15.06637548292112</v>
       </c>
       <c r="F52">
-        <v>2.820820317055384</v>
+        <v>2.519554689800843</v>
       </c>
       <c r="G52">
-        <v>-4.746938842244027</v>
+        <v>-3.183213646102578</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-4.077913895503556</v>
       </c>
       <c r="E53">
-        <v>-17.1340767148234</v>
+        <v>-14.53010000551077</v>
       </c>
       <c r="F53">
-        <v>2.9614058624541</v>
+        <v>2.562073131851736</v>
       </c>
       <c r="G53">
-        <v>-4.568551950943255</v>
+        <v>-4.186640729974807</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-4.142848827260215</v>
       </c>
       <c r="E54">
-        <v>-15.36312185616975</v>
+        <v>-13.85124099549492</v>
       </c>
       <c r="F54">
-        <v>2.520969541324825</v>
+        <v>2.651495392983943</v>
       </c>
       <c r="G54">
-        <v>-4.806017236421829</v>
+        <v>-3.54028273864447</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-4.219128097663335</v>
       </c>
       <c r="E55">
-        <v>-15.64420876629986</v>
+        <v>-12.96908067337871</v>
       </c>
       <c r="F55">
-        <v>2.730465314227625</v>
+        <v>2.415182053782911</v>
       </c>
       <c r="G55">
-        <v>-4.884549993225579</v>
+        <v>-4.978822769849985</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-4.317231412884524</v>
       </c>
       <c r="E56">
-        <v>-15.86817350529721</v>
+        <v>-13.17050719723989</v>
       </c>
       <c r="F56">
-        <v>2.545311945823491</v>
+        <v>2.395929138607045</v>
       </c>
       <c r="G56">
-        <v>-5.115068932662807</v>
+        <v>-3.195646194591314</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.440349983935253</v>
       </c>
       <c r="E57">
-        <v>-15.36036401549908</v>
+        <v>-12.7137336095082</v>
       </c>
       <c r="F57">
-        <v>2.458447683231129</v>
+        <v>2.490063153526375</v>
       </c>
       <c r="G57">
-        <v>-5.054694455969025</v>
+        <v>-4.13662506974419</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.593269645833062</v>
       </c>
       <c r="E58">
-        <v>-14.47918637224253</v>
+        <v>-13.14210913673779</v>
       </c>
       <c r="F58">
-        <v>2.393664382127791</v>
+        <v>2.261864501403168</v>
       </c>
       <c r="G58">
-        <v>-5.809821660773395</v>
+        <v>-3.822024827846191</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.768050916575756</v>
       </c>
       <c r="E59">
-        <v>-14.32803949528852</v>
+        <v>-11.15016927498382</v>
       </c>
       <c r="F59">
-        <v>2.524491759521529</v>
+        <v>2.282563746064322</v>
       </c>
       <c r="G59">
-        <v>-6.528048247920248</v>
+        <v>-4.412336273719652</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.963294316281051</v>
       </c>
       <c r="E60">
-        <v>-14.13230526325498</v>
+        <v>-11.39132410131429</v>
       </c>
       <c r="F60">
-        <v>2.578148429670464</v>
+        <v>2.220306965539522</v>
       </c>
       <c r="G60">
-        <v>-7.102974045901473</v>
+        <v>-4.897773316110141</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-5.164698957342595</v>
       </c>
       <c r="E61">
-        <v>-13.10420128081958</v>
+        <v>-10.80935179269255</v>
       </c>
       <c r="F61">
-        <v>2.810425962885056</v>
+        <v>2.075471895364445</v>
       </c>
       <c r="G61">
-        <v>-6.948008514092018</v>
+        <v>-4.641040697634508</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.367179992974872</v>
       </c>
       <c r="E62">
-        <v>-13.45797925572081</v>
+        <v>-10.46988832412956</v>
       </c>
       <c r="F62">
-        <v>2.379196117070495</v>
+        <v>2.025763224257252</v>
       </c>
       <c r="G62">
-        <v>-6.287751268235874</v>
+        <v>-5.287625093252446</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.557596102660361</v>
       </c>
       <c r="E63">
-        <v>-12.97407558020917</v>
+        <v>-10.83144168890196</v>
       </c>
       <c r="F63">
-        <v>2.118480730917796</v>
+        <v>1.994633177260047</v>
       </c>
       <c r="G63">
-        <v>-6.820431338639247</v>
+        <v>-6.103300679493248</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.729112445174052</v>
       </c>
       <c r="E64">
-        <v>-13.19321749438835</v>
+        <v>-10.54893283793345</v>
       </c>
       <c r="F64">
-        <v>2.098416015687186</v>
+        <v>2.094820901159036</v>
       </c>
       <c r="G64">
-        <v>-7.511850345645438</v>
+        <v>-5.308031010130633</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-5.872829884520331</v>
       </c>
       <c r="E65">
-        <v>-12.60314374576688</v>
+        <v>-10.38379297629573</v>
       </c>
       <c r="F65">
-        <v>2.300642036263018</v>
+        <v>1.78857678581367</v>
       </c>
       <c r="G65">
-        <v>-7.512089874819278</v>
+        <v>-6.187306513858152</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-5.981422908100738</v>
       </c>
       <c r="E66">
-        <v>-12.07189487450505</v>
+        <v>-10.18945351425656</v>
       </c>
       <c r="F66">
-        <v>2.300637066058601</v>
+        <v>2.120140779193006</v>
       </c>
       <c r="G66">
-        <v>-7.855108776643628</v>
+        <v>-6.271735625804224</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.051453036714912</v>
       </c>
       <c r="E67">
-        <v>-12.76826549350857</v>
+        <v>-10.61088689083238</v>
       </c>
       <c r="F67">
-        <v>2.12018054082834</v>
+        <v>2.152347703813851</v>
       </c>
       <c r="G67">
-        <v>-7.692917994960276</v>
+        <v>-6.918871266644149</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.076644739741987</v>
       </c>
       <c r="E68">
-        <v>-12.69899795508724</v>
+        <v>-10.37589531762636</v>
       </c>
       <c r="F68">
-        <v>2.067882393219996</v>
+        <v>2.401441095305273</v>
       </c>
       <c r="G68">
-        <v>-7.487211652955568</v>
+        <v>-6.209723819552278</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.060740809559038</v>
       </c>
       <c r="E69">
-        <v>-12.51434942742448</v>
+        <v>-9.670046602524783</v>
       </c>
       <c r="F69">
-        <v>2.050728561042824</v>
+        <v>1.917217273264016</v>
       </c>
       <c r="G69">
-        <v>-8.389134147886375</v>
+        <v>-7.023742388905561</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.000797919942842</v>
       </c>
       <c r="E70">
-        <v>-12.72164032512559</v>
+        <v>-10.18470767349652</v>
       </c>
       <c r="F70">
-        <v>2.131721355484143</v>
+        <v>1.687141540606065</v>
       </c>
       <c r="G70">
-        <v>-7.759933664090375</v>
+        <v>-6.88382125794616</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-5.906390140238747</v>
       </c>
       <c r="E71">
-        <v>-12.2999307116353</v>
+        <v>-10.37548322649166</v>
       </c>
       <c r="F71">
-        <v>2.140622991594626</v>
+        <v>1.825550136470223</v>
       </c>
       <c r="G71">
-        <v>-8.421713396750102</v>
+        <v>-5.906263324848593</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-5.778766233308281</v>
       </c>
       <c r="E72">
-        <v>-12.35601133374629</v>
+        <v>-9.904218521935425</v>
       </c>
       <c r="F72">
-        <v>1.991987371775505</v>
+        <v>1.985600659099921</v>
       </c>
       <c r="G72">
-        <v>-7.862160121774875</v>
+        <v>-7.520447146131183</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-5.629738464860975</v>
       </c>
       <c r="E73">
-        <v>-12.08153146719337</v>
+        <v>-10.06007501185742</v>
       </c>
       <c r="F73">
-        <v>2.150972613925203</v>
+        <v>1.942557032115653</v>
       </c>
       <c r="G73">
-        <v>-7.882861348593412</v>
+        <v>-6.320415828860146</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.465451377504163</v>
       </c>
       <c r="E74">
-        <v>-12.47561738923688</v>
+        <v>-9.676984224704535</v>
       </c>
       <c r="F74">
-        <v>1.877334696288831</v>
+        <v>2.01741825104145</v>
       </c>
       <c r="G74">
-        <v>-7.336787331784384</v>
+        <v>-7.328252874508268</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.296061279898913</v>
       </c>
       <c r="E75">
-        <v>-12.60098366366522</v>
+        <v>-9.952519225701238</v>
       </c>
       <c r="F75">
-        <v>1.793177538368818</v>
+        <v>1.590265629583468</v>
       </c>
       <c r="G75">
-        <v>-7.814060694934975</v>
+        <v>-6.568955237101846</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.129696842323068</v>
       </c>
       <c r="E76">
-        <v>-12.79317210055075</v>
+        <v>-10.99215270296017</v>
       </c>
       <c r="F76">
-        <v>2.030976968690473</v>
+        <v>1.542821714955529</v>
       </c>
       <c r="G76">
-        <v>-6.93889328059988</v>
+        <v>-5.719545412008392</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.971268716417714</v>
       </c>
       <c r="E77">
-        <v>-12.85263096427146</v>
+        <v>-10.10802249465063</v>
       </c>
       <c r="F77">
-        <v>1.776056840887758</v>
+        <v>1.763341401254786</v>
       </c>
       <c r="G77">
-        <v>-7.920729926610963</v>
+        <v>-6.740120159750279</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.827078127131902</v>
       </c>
       <c r="E78">
-        <v>-13.26845356155179</v>
+        <v>-10.68082464340685</v>
       </c>
       <c r="F78">
-        <v>2.087054128390388</v>
+        <v>1.569786730651459</v>
       </c>
       <c r="G78">
-        <v>-7.109759612086404</v>
+        <v>-5.540512120060409</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.693048504129282</v>
       </c>
       <c r="E79">
-        <v>-13.0389776696871</v>
+        <v>-10.7324537755683</v>
       </c>
       <c r="F79">
-        <v>1.775793420053668</v>
+        <v>1.889296321585256</v>
       </c>
       <c r="G79">
-        <v>-6.769513342479785</v>
+        <v>-5.353144525351438</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-4.570801209034906</v>
       </c>
       <c r="E80">
-        <v>-14.08050404908124</v>
+        <v>-12.10832191942275</v>
       </c>
       <c r="F80">
-        <v>1.914317987354218</v>
+        <v>1.287936378583733</v>
       </c>
       <c r="G80">
-        <v>-6.814899199090024</v>
+        <v>-5.487707421504266</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-4.449622028976503</v>
       </c>
       <c r="E81">
-        <v>-14.37039884115627</v>
+        <v>-11.70241668021922</v>
       </c>
       <c r="F81">
-        <v>1.970088651115098</v>
+        <v>1.22424652245209</v>
       </c>
       <c r="G81">
-        <v>-6.488959055482583</v>
+        <v>-5.146936156448135</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-4.328241224492482</v>
       </c>
       <c r="E82">
-        <v>-15.55384306747679</v>
+        <v>-12.10683657994823</v>
       </c>
       <c r="F82">
-        <v>1.893257574505443</v>
+        <v>1.072237790568769</v>
       </c>
       <c r="G82">
-        <v>-6.223504950101946</v>
+        <v>-5.051806980996714</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-4.196055932964107</v>
       </c>
       <c r="E83">
-        <v>-15.33834204639978</v>
+        <v>-14.01909794153723</v>
       </c>
       <c r="F83">
-        <v>1.637963024636664</v>
+        <v>1.693692270027404</v>
       </c>
       <c r="G83">
-        <v>-5.830782104095127</v>
+        <v>-5.381179282355333</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-4.051464734228917</v>
       </c>
       <c r="E84">
-        <v>-16.87579519979592</v>
+        <v>-14.36553073159802</v>
       </c>
       <c r="F84">
-        <v>1.62312862118733</v>
+        <v>1.146603645787692</v>
       </c>
       <c r="G84">
-        <v>-6.017641109462384</v>
+        <v>-5.154118750441759</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-3.889899952438828</v>
       </c>
       <c r="E85">
-        <v>-16.80590273196154</v>
+        <v>-14.99983408585241</v>
       </c>
       <c r="F85">
-        <v>1.521027368587875</v>
+        <v>1.174599150532704</v>
       </c>
       <c r="G85">
-        <v>-5.369347197411976</v>
+        <v>-4.386873994418361</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-3.713168953265001</v>
       </c>
       <c r="E86">
-        <v>-18.76576741231917</v>
+        <v>-15.80226609458957</v>
       </c>
       <c r="F86">
-        <v>1.542564921060662</v>
+        <v>1.010035682292555</v>
       </c>
       <c r="G86">
-        <v>-5.362266321286694</v>
+        <v>-4.257839956593197</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-3.525932934686133</v>
       </c>
       <c r="E87">
-        <v>-18.92623841725498</v>
+        <v>-18.71897469039791</v>
       </c>
       <c r="F87">
-        <v>1.433016645510038</v>
+        <v>1.19629906301644</v>
       </c>
       <c r="G87">
-        <v>-5.432402432119825</v>
+        <v>-4.481927701773915</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-3.336406200001626</v>
       </c>
       <c r="E88">
-        <v>-20.40585390062516</v>
+        <v>-17.64804040079796</v>
       </c>
       <c r="F88">
-        <v>1.504566051559443</v>
+        <v>1.251446794490415</v>
       </c>
       <c r="G88">
-        <v>-5.523699140789815</v>
+        <v>-3.346260826612945</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-3.159618691152092</v>
       </c>
       <c r="E89">
-        <v>-20.71351842470628</v>
+        <v>-18.85453455981753</v>
       </c>
       <c r="F89">
-        <v>1.31058062990666</v>
+        <v>0.8037423777689769</v>
       </c>
       <c r="G89">
-        <v>-4.663733625939628</v>
+        <v>-4.41045285254453</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-3.007751574123188</v>
       </c>
       <c r="E90">
-        <v>-22.73906409207117</v>
+        <v>-21.18300796745151</v>
       </c>
       <c r="F90">
-        <v>1.088757093315397</v>
+        <v>0.5432158593841157</v>
       </c>
       <c r="G90">
-        <v>-4.884405619476963</v>
+        <v>-4.170277278057855</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-2.900411652007797</v>
       </c>
       <c r="E91">
-        <v>-23.19775775278211</v>
+        <v>-23.34761854311794</v>
       </c>
       <c r="F91">
-        <v>0.9897340539847443</v>
+        <v>0.6512730736097</v>
       </c>
       <c r="G91">
-        <v>-5.041799255240408</v>
+        <v>-3.657294380675828</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-2.846718211526314</v>
       </c>
       <c r="E92">
-        <v>-25.95354249625387</v>
+        <v>-24.46087142231957</v>
       </c>
       <c r="F92">
-        <v>0.722113397162308</v>
+        <v>1.179720117816811</v>
       </c>
       <c r="G92">
-        <v>-4.42120869681639</v>
+        <v>-3.276298620522465</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-2.863808919869546</v>
       </c>
       <c r="E93">
-        <v>-28.11467973235642</v>
+        <v>-27.60269498952321</v>
       </c>
       <c r="F93">
-        <v>0.5050314355846697</v>
+        <v>0.8331527340379706</v>
       </c>
       <c r="G93">
-        <v>-4.605153977438861</v>
+        <v>-3.362847401595938</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-2.953652818338607</v>
       </c>
       <c r="E94">
-        <v>-29.93912266175167</v>
+        <v>-27.931412389266</v>
       </c>
       <c r="F94">
-        <v>0.7658197180688155</v>
+        <v>0.8054753223756336</v>
       </c>
       <c r="G94">
-        <v>-4.224437121118051</v>
+        <v>-3.687550524675468</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-3.123586721932523</v>
       </c>
       <c r="E95">
-        <v>-31.34711806445354</v>
+        <v>-31.03654173158549</v>
       </c>
       <c r="F95">
-        <v>0.7975412193916198</v>
+        <v>0.2425814480905079</v>
       </c>
       <c r="G95">
-        <v>-4.745357293452375</v>
+        <v>-3.47221051617223</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-3.369709968628941</v>
       </c>
       <c r="E96">
-        <v>-33.30234558742732</v>
+        <v>-32.74770714791587</v>
       </c>
       <c r="F96">
-        <v>0.398206832054451</v>
+        <v>0.3921837726686958</v>
       </c>
       <c r="G96">
-        <v>-4.574553305175479</v>
+        <v>-3.830638034439733</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-3.681719078790121</v>
       </c>
       <c r="E97">
-        <v>-35.85831141531063</v>
+        <v>-35.71585241574033</v>
       </c>
       <c r="F97">
-        <v>0.05344943105072755</v>
+        <v>0.1630341547670741</v>
       </c>
       <c r="G97">
-        <v>-4.540523756382479</v>
+        <v>-3.716034809033008</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-4.053027306743106</v>
       </c>
       <c r="E98">
-        <v>-38.49235039932318</v>
+        <v>-37.45343694943146</v>
       </c>
       <c r="F98">
-        <v>0.1640207403438084</v>
+        <v>0.09932193271555577</v>
       </c>
       <c r="G98">
-        <v>-4.408733492447381</v>
+        <v>-3.251928988000469</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-4.45350209378341</v>
       </c>
       <c r="E99">
-        <v>-41.47632268380445</v>
+        <v>-40.42618993955873</v>
       </c>
       <c r="F99">
-        <v>-0.09468833995931084</v>
+        <v>0.03611584314714789</v>
       </c>
       <c r="G99">
-        <v>-5.043955017804962</v>
+        <v>-3.753801669182216</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-4.885956335163526</v>
       </c>
       <c r="E100">
-        <v>-42.49603540390365</v>
+        <v>-42.98092402251196</v>
       </c>
       <c r="F100">
-        <v>-0.1621207600168018</v>
+        <v>-0.2257609141042766</v>
       </c>
       <c r="G100">
-        <v>-5.18460786117212</v>
+        <v>-3.915247613571575</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-5.29477916604539</v>
       </c>
       <c r="E101">
-        <v>-45.47209644429352</v>
+        <v>-46.01309512009387</v>
       </c>
       <c r="F101">
-        <v>-0.2400129752694421</v>
+        <v>-0.4927892882337113</v>
       </c>
       <c r="G101">
-        <v>-5.448713384491825</v>
+        <v>-4.226402572832158</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-5.725066454823939</v>
       </c>
       <c r="E102">
-        <v>-48.39680458943641</v>
+        <v>-47.41013161569717</v>
       </c>
       <c r="F102">
-        <v>-0.2482370068444356</v>
+        <v>-0.09942991497293521</v>
       </c>
       <c r="G102">
-        <v>-5.561101785345925</v>
+        <v>-3.451906317162386</v>
       </c>
     </row>
   </sheetData>
